--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Escritorio\Cuarto\TFG (CTC)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2069F049-CFB8-4C82-8B2D-CD218B3A4208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F3428D2-7D76-4CB1-8791-1FD2F99C6518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Nº semana</t>
   </si>
@@ -72,6 +72,18 @@
   </si>
   <si>
     <t>Tarea 4. Conclusiones y redacción</t>
+  </si>
+  <si>
+    <t>T.2.2 Entrenamiento de los modelos</t>
+  </si>
+  <si>
+    <t>T.2.3 Optimización de parámetros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.2.4 Resultados del modelaje </t>
+  </si>
+  <si>
+    <t>T.2.1 Preparación de los datasets</t>
   </si>
 </sst>
 </file>
@@ -860,7 +872,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -909,14 +921,16 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="28"/>
+      <c r="B12" s="28" t="s">
+        <v>15</v>
+      </c>
       <c r="C12" s="28"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="8"/>
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
       <c r="L12" s="7"/>
@@ -935,16 +949,18 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="28"/>
+      <c r="B13" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="C13" s="28"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -961,7 +977,9 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="28"/>
+      <c r="B14" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="C14" s="28"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -971,8 +989,8 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
       <c r="N14" s="7"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -987,7 +1005,9 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
+      <c r="B15" s="28" t="s">
+        <v>14</v>
+      </c>
       <c r="C15" s="28"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -999,8 +1019,8 @@
       <c r="K15" s="8"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="8"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1048,7 +1068,7 @@
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
+      <c r="I17" s="8"/>
       <c r="J17" s="7"/>
       <c r="K17" s="8"/>
       <c r="L17" s="7"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F3428D2-7D76-4CB1-8791-1FD2F99C6518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{167EBBBD-2AC8-4E54-BAEA-E63F4E5CF228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,6 +253,24 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -276,23 +294,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,46 +730,46 @@
       <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="30">
         <v>45964</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="19">
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="25">
         <v>45994</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="19">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="25">
         <v>46025</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="19">
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="25">
         <v>46056</v>
       </c>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="19">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="25">
         <v>46084</v>
       </c>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="17" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="18"/>
+      <c r="Y5" s="24"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -785,10 +794,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -812,10 +821,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -839,10 +848,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -893,10 +902,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="25"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -921,16 +930,16 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="8"/>
+      <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
       <c r="L12" s="7"/>
@@ -949,10 +958,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -961,8 +970,8 @@
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -977,10 +986,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -989,9 +998,9 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="13"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="13"/>
-      <c r="N14" s="7"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -1005,10 +1014,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1019,7 +1028,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="13"/>
+      <c r="N15" s="8"/>
       <c r="O15" s="13"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -1033,10 +1042,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="16"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1061,8 +1070,8 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -1087,8 +1096,8 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -1113,8 +1122,8 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -1139,8 +1148,8 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1165,8 +1174,8 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1191,10 +1200,10 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="16"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1219,8 +1228,8 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1245,8 +1254,8 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1271,8 +1280,8 @@
       <c r="Y24" s="3"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -1297,8 +1306,8 @@
       <c r="Y25" s="3"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1323,8 +1332,8 @@
       <c r="Y26" s="3"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1376,17 +1385,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="L5:O5"/>
@@ -1403,6 +1401,17 @@
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
     <mergeCell ref="T5:W5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Escritorio\Cuarto\TFG (CTC)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{167EBBBD-2AC8-4E54-BAEA-E63F4E5CF228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B80829F-397C-40FC-9D9C-F2851F6C8F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
@@ -910,7 +910,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="5"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -938,7 +938,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="6"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
@@ -967,8 +967,8 @@
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="8"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Escritorio\Cuarto\TFG (CTC)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B80829F-397C-40FC-9D9C-F2851F6C8F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBAC370D-766F-478B-AF3A-F4AA2075AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="1236" yWindow="552" windowWidth="19704" windowHeight="10392" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -199,31 +199,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -243,8 +223,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -253,23 +231,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -288,20 +254,29 @@
     <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE070019-53EE-4844-AC8E-2EA67398FEB4}">
-  <dimension ref="B4:AA28"/>
+  <dimension ref="B4:AA24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="70.109375" bestFit="1" customWidth="1"/>
@@ -651,125 +626,125 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>2</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>3</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="11">
         <v>4</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="11">
         <v>5</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="11">
         <v>6</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="11">
         <v>7</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="11">
         <v>8</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="11">
         <v>9</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="11">
         <v>10</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="11">
         <v>11</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="11">
         <v>12</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="11">
         <v>13</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="11">
         <v>14</v>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="11">
         <v>15</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="11">
         <v>16</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="11">
         <v>17</v>
       </c>
-      <c r="U4" s="13">
+      <c r="U4" s="11">
         <v>18</v>
       </c>
-      <c r="V4" s="13">
+      <c r="V4" s="11">
         <v>19</v>
       </c>
-      <c r="W4" s="13">
+      <c r="W4" s="11">
         <v>20</v>
       </c>
-      <c r="X4" s="13">
+      <c r="X4" s="11">
         <v>21</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="Y4" s="11">
         <v>22</v>
       </c>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="22">
         <v>45964</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="25">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="19">
         <v>45994</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="25">
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="19">
         <v>46025</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="25">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="19">
         <v>46056</v>
       </c>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="25">
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="19">
         <v>46084</v>
       </c>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="23" t="s">
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="24"/>
+      <c r="Y5" s="18"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -794,10 +769,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="20"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -821,10 +796,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="20"/>
+      <c r="C8" s="29"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -848,10 +823,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="20"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -875,7 +850,7 @@
       <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="7"/>
@@ -902,10 +877,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -930,10 +905,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -958,10 +933,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -969,9 +944,9 @@
       <c r="H13" s="7"/>
       <c r="I13" s="4"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="8"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -986,10 +961,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -999,8 +974,8 @@
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="11"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -1014,10 +989,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1029,7 +1004,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="8"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="11"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1042,10 +1017,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1070,8 +1045,8 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -1096,8 +1071,8 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -1122,8 +1097,8 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -1148,34 +1123,36 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
+      <c r="B20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="16"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
       <c r="K20" s="8"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1200,10 +1177,8 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="22"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1220,16 +1195,16 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1254,8 +1229,8 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1279,122 +1254,14 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="B22:C22"/>
+  <mergeCells count="24">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="P5:S5"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
@@ -1402,16 +1269,17 @@
     <mergeCell ref="H5:K5"/>
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Escritorio\Cuarto\TFG (CTC)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBAC370D-766F-478B-AF3A-F4AA2075AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9421E95-F1CE-4D78-A288-DB36D6482F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1236" yWindow="552" windowWidth="19704" windowHeight="10392" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -943,8 +943,8 @@
       <c r="G13" s="8"/>
       <c r="H13" s="7"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="11"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="6"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="7"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Escritorio\Cuarto\TFG (CTC)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9421E95-F1CE-4D78-A288-DB36D6482F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22163C90-A15C-47DA-B7D7-94535C6870BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="0" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -239,21 +239,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -277,6 +262,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -705,46 +705,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="17">
         <v>45964</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="19">
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="17">
         <v>45994</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="19">
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="27">
         <v>46025</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="19">
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="27">
         <v>46056</v>
       </c>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="19">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="27">
         <v>46084</v>
       </c>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="17" t="s">
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="18"/>
+      <c r="Y5" s="26"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -769,10 +769,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -796,10 +796,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -823,10 +823,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -877,10 +877,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -905,10 +905,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -933,10 +933,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -944,9 +944,9 @@
       <c r="H13" s="7"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="6"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -961,10 +961,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -989,10 +989,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1256,18 +1256,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="P5:S5"/>
+    <mergeCell ref="T5:W5"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="T5:W5"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
@@ -1275,6 +1272,9 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B22:C22"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22163C90-A15C-47DA-B7D7-94535C6870BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E176878-7DF5-4446-97D9-946E294DA5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="1476" yWindow="768" windowWidth="20664" windowHeight="10032" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -231,53 +231,53 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,46 +705,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="20">
         <v>45964</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="17">
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="20">
         <v>45994</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="27">
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="15">
         <v>46025</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="27">
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="15">
         <v>46056</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="27">
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="15">
         <v>46084</v>
       </c>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="25" t="s">
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="26"/>
+      <c r="Y5" s="14"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -769,10 +769,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -796,10 +796,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -823,10 +823,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -877,10 +877,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="21"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -905,10 +905,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="23"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -933,10 +933,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -946,7 +946,7 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="6"/>
+      <c r="M13" s="4"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -961,10 +961,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -975,7 +975,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="11"/>
+      <c r="N14" s="6"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -989,10 +989,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="23"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1017,10 +1017,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="16"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1045,8 +1045,8 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -1071,8 +1071,8 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -1097,8 +1097,8 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -1123,10 +1123,10 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="16"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1151,8 +1151,8 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1177,8 +1177,8 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1203,8 +1203,8 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1229,8 +1229,8 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1256,6 +1256,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="P5:S5"/>
@@ -1272,14 +1280,6 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E176878-7DF5-4446-97D9-946E294DA5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FBC1E8C-F483-499A-A24A-90C82206ED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1476" yWindow="768" windowWidth="20664" windowHeight="10032" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Nº semana</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>T.2.1 Preparación de los datasets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  T.3.1 Comprobar overfitting y validar resultados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  T.4.1 Redactar memoria</t>
   </si>
 </sst>
 </file>
@@ -107,7 +113,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,8 +144,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -199,11 +223,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -231,40 +275,63 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -276,8 +343,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE070019-53EE-4844-AC8E-2EA67398FEB4}">
-  <dimension ref="B4:AA24"/>
+  <dimension ref="B4:AA19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="70.109375" bestFit="1" customWidth="1"/>
@@ -705,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="31">
         <v>45964</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="20">
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="22">
         <v>45994</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="15">
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="22">
         <v>46025</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="15">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="25">
         <v>46056</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="15">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="28">
         <v>46084</v>
       </c>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="13" t="s">
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="14"/>
+      <c r="Y5" s="21"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="25"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -769,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -796,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -823,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -877,22 +946,22 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -905,15 +974,15 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="26"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="4"/>
+      <c r="H12" s="16"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
@@ -933,20 +1002,20 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="37"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -961,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -989,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1004,7 +1073,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="8"/>
-      <c r="O15" s="11"/>
+      <c r="O15" s="7"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1017,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="29"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1033,10 +1102,10 @@
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="8"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
@@ -1045,8 +1114,10 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
+      <c r="B17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="13"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -1059,227 +1130,92 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
+      <c r="B18" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="17">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="P5:S5"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="H5:K5"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="P5:S5"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FBC1E8C-F483-499A-A24A-90C82206ED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{088CAFF7-4DF9-42F6-9197-5D24FB2D4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="1116" yWindow="852" windowWidth="20664" windowHeight="10032" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,6 +286,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -328,25 +334,19 @@
     <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <v>45964</v>
       </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="22">
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="24">
         <v>45994</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="22">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="24">
         <v>46025</v>
       </c>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="25">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27">
         <v>46056</v>
       </c>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="28">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30">
         <v>46084</v>
       </c>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="20" t="s">
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="21"/>
+      <c r="Y5" s="23"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="37"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="37"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1044,7 +1044,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="16"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1073,7 +1073,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="8"/>
-      <c r="O15" s="7"/>
+      <c r="O15" s="16"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1130,7 +1130,7 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8"/>
-      <c r="P17" s="3"/>
+      <c r="P17" s="6"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="42"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{088CAFF7-4DF9-42F6-9197-5D24FB2D4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{066184CE-0478-4D2C-B54F-40D6C3DF2CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="852" windowWidth="20664" windowHeight="10032" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="864" yWindow="924" windowWidth="21132" windowHeight="10428" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,56 +286,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -346,6 +301,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="40">
         <v>45964</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="24">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="31">
         <v>45994</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="24">
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="31">
         <v>46025</v>
       </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="27">
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="34">
         <v>46056</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="30">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37">
         <v>46084</v>
       </c>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="22" t="s">
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23"/>
+      <c r="Y5" s="30"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="38"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="38"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="40"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1130,8 +1130,8 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="3"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="6"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1199,13 +1199,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1216,6 +1209,13 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{066184CE-0478-4D2C-B54F-40D6C3DF2CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA670E19-1761-4382-9277-800EB9F5F92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="924" windowWidth="21132" windowHeight="10428" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="1908" yWindow="348" windowWidth="21132" windowHeight="10428" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,11 +286,56 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -301,51 +346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="33">
         <v>45964</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="31">
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="24">
         <v>45994</v>
       </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="31">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="24">
         <v>46025</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="34">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27">
         <v>46056</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="37">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30">
         <v>46084</v>
       </c>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="29" t="s">
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="30"/>
+      <c r="Y5" s="23"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1131,8 +1131,8 @@
       <c r="N17" s="7"/>
       <c r="O17" s="8"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="3"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="6"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1199,6 +1199,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1209,13 +1216,6 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA670E19-1761-4382-9277-800EB9F5F92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37C17AA7-1F40-49D6-9597-FA2397BC62AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1908" yWindow="348" windowWidth="21132" windowHeight="10428" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="252" yWindow="252" windowWidth="21132" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1132,8 +1132,8 @@
       <c r="O17" s="8"/>
       <c r="P17" s="18"/>
       <c r="Q17" s="18"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="3"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="6"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37C17AA7-1F40-49D6-9597-FA2397BC62AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C3889C-4532-4D16-ABBF-0F3099D62BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="252" yWindow="252" windowWidth="21132" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="0" yWindow="948" windowWidth="23040" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,56 +286,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -346,6 +301,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="40">
         <v>45964</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="24">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="31">
         <v>45994</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="24">
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="31">
         <v>46025</v>
       </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="27">
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="34">
         <v>46056</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="30">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37">
         <v>46084</v>
       </c>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="22" t="s">
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23"/>
+      <c r="Y5" s="30"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="38"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="38"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="40"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1133,7 +1133,7 @@
       <c r="P17" s="18"/>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
-      <c r="S17" s="6"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1190,7 +1190,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="T19" s="6"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -1199,13 +1199,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1216,6 +1209,13 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C3889C-4532-4D16-ABBF-0F3099D62BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4461595D-5EC3-450D-9700-317DB4F0C627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="948" windowWidth="23040" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="0" yWindow="1644" windowWidth="23040" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,11 +286,56 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -301,51 +346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="33">
         <v>45964</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="31">
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="24">
         <v>45994</v>
       </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="31">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="24">
         <v>46025</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="34">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27">
         <v>46056</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="37">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30">
         <v>46084</v>
       </c>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="29" t="s">
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="30"/>
+      <c r="Y5" s="23"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1190,8 +1190,8 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="3"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="6"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
@@ -1199,6 +1199,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1209,13 +1216,6 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4461595D-5EC3-450D-9700-317DB4F0C627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22F3270-0834-4490-90D7-95AEA3C2AE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1644" windowWidth="23040" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -286,56 +286,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -346,6 +301,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="40">
         <v>45964</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="24">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="31">
         <v>45994</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="24">
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="31">
         <v>46025</v>
       </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="27">
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="34">
         <v>46056</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="30">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37">
         <v>46084</v>
       </c>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="22" t="s">
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="23"/>
+      <c r="Y5" s="30"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="38"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="38"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="40"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1191,21 +1191,14 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="19"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="6"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1216,6 +1209,13 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22F3270-0834-4490-90D7-95AEA3C2AE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48100E5-C92B-4FAE-86E2-82F97BFAA806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
@@ -286,11 +286,56 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -301,51 +346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,46 +774,46 @@
       <c r="C5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="33">
         <v>45964</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="31">
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="24">
         <v>45994</v>
       </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="31">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="24">
         <v>46025</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="34">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27">
         <v>46056</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="37">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30">
         <v>46084</v>
       </c>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="29" t="s">
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="Y5" s="30"/>
+      <c r="Y5" s="23"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -838,10 +838,10 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -865,10 +865,10 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="7"/>
       <c r="E8" s="4"/>
       <c r="G8" s="8"/>
@@ -892,10 +892,10 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
@@ -946,10 +946,10 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -974,10 +974,10 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1002,10 +1002,10 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1030,10 +1030,10 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -1058,10 +1058,10 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -1086,10 +1086,10 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -1142,10 +1142,10 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1192,13 +1192,20 @@
       <c r="S19" s="3"/>
       <c r="T19" s="19"/>
       <c r="U19" s="19"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="3"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="6"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -1209,13 +1216,6 @@
     <mergeCell ref="T5:W5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guill\OneDrive\Documentos\GitHub\TFG---IA-DE-PREDICCI-N-FOTOVOLTAICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48100E5-C92B-4FAE-86E2-82F97BFAA806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E834E24-D6CC-450D-A106-AD8F4988DF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
+    <workbookView xWindow="0" yWindow="1812" windowWidth="23040" windowHeight="10428" tabRatio="167" xr2:uid="{484CA3C8-3C5E-4DD8-84DA-D9F18CB2C1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1193,9 +1193,9 @@
       <c r="T19" s="19"/>
       <c r="U19" s="19"/>
       <c r="V19" s="19"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="17">
